--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:01</t>
+    <t xml:space="preserve">2026-09-10 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:12</t>
+    <t xml:space="preserve">2026-09-12 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:24</t>
+    <t xml:space="preserve">2026-09-23 23:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:53</t>
+    <t xml:space="preserve">2026-10-02 15:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:47</t>
+    <t xml:space="preserve">2026-10-05 16:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
